--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486943_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486943_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2712</v>
+        <v>3.8098</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6277</v>
+        <v>2.2554</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6434</v>
+        <v>1.5545</v>
       </c>
       <c r="G2" t="n">
         <v>2.1673</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5121</v>
+        <v>-0.9734</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7827</v>
+        <v>-0.1551</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7294</v>
+        <v>-0.8183</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2168</v>
+        <v>0.8454</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8378</v>
+        <v>-0.9424</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0546</v>
+        <v>1.7878</v>
       </c>
       <c r="G3" t="n">
         <v>0.8282</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5467</v>
+        <v>0.1754</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1858</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3609</v>
+        <v>0.0941</v>
       </c>
       <c r="V3" t="n">
         <v>0.4579</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SÁNCHEZ</t>
+          <t>P. SALO BLAYA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4153</v>
+        <v>0.3068</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8545</v>
+        <v>0.6834</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4393</v>
+        <v>-0.3766</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7198</v>
+        <v>1.2229</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0172</v>
+        <v>1.7517</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2974</v>
+        <v>-0.5288</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3192</v>
+        <v>1.9357</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5958</v>
+        <v>1.3042</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2766</v>
+        <v>0.6315</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.7127</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4214</v>
+        <v>0.4475</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0208</v>
+        <v>-1.1602</v>
       </c>
       <c r="P4" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.8214</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-1.0267</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.8481</v>
-      </c>
       <c r="S4" t="n">
-        <v>-0.358</v>
+        <v>-0.5938</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0272</v>
+        <v>-0.3488</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3307</v>
+        <v>-0.245</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7679</v>
+        <v>-0.9384</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5893</v>
+        <v>-0.6982</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SALO BLAYA</t>
+          <t>J. SÁNCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.054</v>
+        <v>-0.0171</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5788</v>
+        <v>1.5407</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5248</v>
+        <v>-1.5578</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2229</v>
+        <v>1.7198</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7517</v>
+        <v>3.0172</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5288</v>
+        <v>-1.2974</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9357</v>
+        <v>2.3192</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3042</v>
+        <v>2.5958</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6315</v>
+        <v>-0.2766</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7127</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4475</v>
+        <v>0.4214</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1602</v>
+        <v>-1.0208</v>
       </c>
       <c r="P5" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8466</v>
+        <v>-0.7904</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4534</v>
+        <v>-0.341</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3932</v>
+        <v>-0.4493</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9384</v>
+        <v>-1.7679</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6982</v>
+        <v>0.5893</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1946</v>
+        <v>-0.0743</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4291</v>
+        <v>-0.2199</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2345</v>
+        <v>0.1456</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4333</v>
@@ -922,13 +922,13 @@
         <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8148</v>
+        <v>-0.6945</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.527</v>
+        <v>-0.3178</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2878</v>
+        <v>-0.3767</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5893</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5254</v>
+        <v>-0.9421</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8903</v>
+        <v>-1.0995</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3649</v>
+        <v>0.1574</v>
       </c>
       <c r="G7" t="n">
         <v>-2.1348</v>
@@ -1000,13 +1000,13 @@
         <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0066</v>
+        <v>-0.4233</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2249</v>
+        <v>-0.4341</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2183</v>
+        <v>0.0108</v>
       </c>
       <c r="V7" t="n">
         <v>0.5893</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5136</v>
+        <v>-1.5153</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2546</v>
+        <v>-1.4638</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.259</v>
+        <v>-0.0515</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6255</v>
@@ -1078,13 +1078,13 @@
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2023</v>
+        <v>-1.204</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2907</v>
+        <v>-0.4999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9116</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0.6982</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3848</v>
+        <v>-2.0727</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4419</v>
+        <v>-1.3373</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9429</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1705</v>
@@ -1156,13 +1156,13 @@
         <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2759</v>
+        <v>-0.9638</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3411</v>
+        <v>-0.2365</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9347</v>
+        <v>-0.7272</v>
       </c>
       <c r="V9" t="n">
         <v>0.2402</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7612</v>
+        <v>-3.7918</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.148</v>
+        <v>-3.4158</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6132</v>
+        <v>-0.3761</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5241</v>
@@ -1234,13 +1234,13 @@
         <v>2.4641</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8799</v>
+        <v>-0.9105</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1044</v>
+        <v>-0.3722</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7755</v>
+        <v>-0.5384</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5893</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4873</v>
+        <v>-6.4584</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0771</v>
+        <v>-7.0185</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5898</v>
+        <v>0.5601</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8395</v>
@@ -1312,13 +1312,13 @@
         <v>2.8748</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8984</v>
+        <v>-0.0727</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9877</v>
+        <v>0.0463</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0893</v>
+        <v>-0.1189</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1088</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.909600000000001</v>
+        <v>-9.909700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.0178</v>
+        <v>-11.0177</v>
       </c>
       <c r="F12" t="n">
         <v>1.108</v>
@@ -1390,13 +1390,13 @@
         <v>19.5074</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.4511</v>
+        <v>-6.451</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.577900000000001</v>
+        <v>-2.5779</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.873</v>
+        <v>-3.872999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8295000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.296</v>
+        <v>11.4502</v>
       </c>
       <c r="E13" t="n">
-        <v>8.579700000000001</v>
+        <v>8.6843</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7163</v>
+        <v>2.766</v>
       </c>
       <c r="G13" t="n">
         <v>6.6421</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3194</v>
+        <v>0.8349</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5615</v>
+        <v>0.6662</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8809</v>
+        <v>0.1687</v>
       </c>
       <c r="V13" t="n">
         <v>2.9466</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5968</v>
+        <v>5.3554</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1848</v>
+        <v>3.1388</v>
       </c>
       <c r="F14" t="n">
-        <v>2.412</v>
+        <v>2.2166</v>
       </c>
       <c r="G14" t="n">
         <v>4.36</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5858</v>
+        <v>1.3445</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5728</v>
+        <v>0.5268</v>
       </c>
       <c r="U14" t="n">
-        <v>1.013</v>
+        <v>0.8177</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3491</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7334</v>
+        <v>1.6433</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4587</v>
+        <v>0.2352</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2746</v>
+        <v>1.408</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8147</v>
+        <v>0.8006</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5147</v>
+        <v>0.24</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>0.5606</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3969</v>
+        <v>0.3554</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5153</v>
+        <v>0.237</v>
       </c>
       <c r="L15" t="n">
         <v>0.1184</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4177</v>
+        <v>0.4452</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9994</v>
+        <v>0.003</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5816</v>
+        <v>0.4422</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5829</v>
+        <v>0.432</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4019</v>
+        <v>0.0852</v>
       </c>
       <c r="U15" t="n">
-        <v>0.181</v>
+        <v>0.3468</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>K. OBIEKWE SAM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2562</v>
+        <v>1.296</v>
       </c>
       <c r="E16" t="n">
-        <v>0.026</v>
+        <v>0.4655</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2302</v>
+        <v>0.8305</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8006</v>
+        <v>0.1072</v>
       </c>
       <c r="H16" t="n">
-        <v>0.24</v>
+        <v>0.5256</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5606</v>
+        <v>-0.4184</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3554</v>
+        <v>0.2175</v>
       </c>
       <c r="K16" t="n">
-        <v>0.237</v>
+        <v>0.9149</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1184</v>
+        <v>-0.6974</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4452</v>
+        <v>-0.1104</v>
       </c>
       <c r="N16" t="n">
-        <v>0.003</v>
+        <v>-0.3893</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4422</v>
+        <v>0.2789</v>
       </c>
       <c r="P16" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>0.045</v>
+        <v>0.4291</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.124</v>
+        <v>0.2479</v>
       </c>
       <c r="U16" t="n">
-        <v>0.169</v>
+        <v>0.1811</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. OBIEKWE SAM</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0514</v>
+        <v>0.18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1517</v>
+        <v>-0.0057</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.1857</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1072</v>
+        <v>-0.8147</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5256</v>
+        <v>-1.5147</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4184</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2175</v>
+        <v>-0.3969</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9149</v>
+        <v>-0.5153</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6974</v>
+        <v>0.1184</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1104</v>
+        <v>-0.4177</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3893</v>
+        <v>-0.9994</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2789</v>
+        <v>0.5816</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1844</v>
+        <v>1.0296</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0659</v>
+        <v>0.9375</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2503</v>
+        <v>0.0921</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3491</v>
+        <v>-0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3491</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3808</v>
+        <v>-0.1538</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.689</v>
+        <v>-0.1322</v>
       </c>
       <c r="F18" t="n">
-        <v>4.0698</v>
+        <v>-0.0216</v>
       </c>
       <c r="G18" t="n">
-        <v>0.82</v>
+        <v>1.1468</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6747</v>
+        <v>-0.8081</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4947</v>
+        <v>1.9549</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0151</v>
+        <v>1.6772</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.765</v>
+        <v>0.4672</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7498</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8351</v>
+        <v>-0.5305</v>
       </c>
       <c r="N18" t="n">
-        <v>0.09030000000000001</v>
+        <v>-1.2753</v>
       </c>
       <c r="O18" t="n">
         <v>0.7449</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.8748</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.1336</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2588</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4828</v>
+        <v>0.4592</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9176</v>
+        <v>0.0038</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5652</v>
+        <v>0.4554</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0472</v>
+        <v>-0.9384</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.4579</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5893</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6594</v>
+        <v>-0.8868</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6552</v>
+        <v>-4.3166</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0042</v>
+        <v>3.4298</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1468</v>
+        <v>0.82</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8081</v>
+        <v>-0.6747</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9549</v>
+        <v>1.4947</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6772</v>
+        <v>-0.0151</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4672</v>
+        <v>-0.765</v>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>0.7498</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5305</v>
+        <v>0.8351</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2753</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>0.7449</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8214</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-5.1336</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0464</v>
+        <v>2.2153</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5192</v>
+        <v>1.29</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4729</v>
+        <v>0.9253</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9384</v>
+        <v>-1.0472</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>-0.4579</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1786</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1987</v>
+        <v>-1.5337</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7179</v>
+        <v>-3.7764</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5192</v>
+        <v>2.2428</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7985</v>
@@ -2014,13 +2014,13 @@
         <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1332</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5038</v>
+        <v>0.4376</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6294</v>
+        <v>0.0941</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6193</v>
+        <v>-2.9286</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8267</v>
+        <v>-2.888</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7926</v>
+        <v>-0.0406</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4213</v>
+        <v>-1.0528</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.0735</v>
+        <v>-3.5261</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6522</v>
+        <v>2.4733</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8042</v>
+        <v>0.0907</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.7115</v>
+        <v>-1.7772</v>
       </c>
       <c r="L21" t="n">
-        <v>1.9074</v>
+        <v>1.8679</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6171</v>
+        <v>-1.1435</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.362</v>
+        <v>-1.7489</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7449</v>
+        <v>0.6054</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.616</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2321</v>
+        <v>-4.3122</v>
       </c>
       <c r="R21" t="n">
-        <v>0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.582</v>
+        <v>0.6499</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7905</v>
+        <v>0.1548</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2085</v>
+        <v>0.4951</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9276</v>
+        <v>-3.0683</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6202</v>
+        <v>-2.5129</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3074</v>
+        <v>-0.5555</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0528</v>
+        <v>-2.4213</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.5261</v>
+        <v>-5.0735</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4733</v>
+        <v>2.6522</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0907</v>
+        <v>-0.8042</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.7772</v>
+        <v>-2.7115</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8679</v>
+        <v>1.9074</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1435</v>
+        <v>-1.6171</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7489</v>
+        <v>-2.362</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6054</v>
+        <v>0.7449</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.8748</v>
+        <v>-0.616</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.3122</v>
+        <v>-1.2321</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4374</v>
+        <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3491</v>
+        <v>-0.031</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5774</v>
+        <v>-0.4767</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2283</v>
+        <v>0.4457</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.909599999999999</v>
+        <v>11.3537</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.108099999999998</v>
+        <v>-1.108000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>11.0176</v>
+        <v>12.4617</v>
       </c>
       <c r="G23" t="n">
         <v>8.789400000000001</v>
@@ -2224,7 +2224,7 @@
         <v>9.898100000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5069000000000006</v>
+        <v>0.5069000000000008</v>
       </c>
       <c r="L23" t="n">
         <v>9.3912</v>
@@ -2239,7 +2239,7 @@
         <v>8.7247</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.160300000000001</v>
+        <v>-6.160299999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-19.5076</v>
@@ -2248,13 +2248,13 @@
         <v>13.3474</v>
       </c>
       <c r="S23" t="n">
-        <v>6.4508</v>
+        <v>7.895300000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>3.873</v>
+        <v>3.8731</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5779</v>
+        <v>4.022</v>
       </c>
       <c r="V23" t="n">
         <v>0.8296999999999999</v>
